--- a/results/Int All Data 0.6/Linea_fi_all.xlsx
+++ b/results/Int All Data 0.6/Linea_fi_all.xlsx
@@ -1346,7 +1346,7 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>-0.0015873015873015817 +/- 0.0005815574342857539</t>
+          <t>-0.0014848950332821188 +/- 0.0005815574342857567</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="EJ2" t="inlineStr">
         <is>
-          <t>-0.0001536098310291778 +/- 0.0003278609440569643</t>
+          <t>-0.00010240655401945186 +/- 0.00030721966205835564</t>
         </is>
       </c>
       <c r="EK2" t="inlineStr">
         <is>
-          <t>-0.00025601638504862967 +/- 0.0011953525376271305</t>
+          <t>-0.0003072196620583556 +/- 0.0012160104543817787</t>
         </is>
       </c>
       <c r="EL2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>0.008110936682365233 +/- 0.0025874903851546022</t>
+          <t>0.008163265306122436 +/- 0.0026497098694237995</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>0.0038723181580324283 +/- 0.0011026325225382257</t>
+          <t>0.0038199895342752367 +/- 0.0011235432000828815</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -2391,7 +2391,7 @@
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>0.00010465724751438366 +/- 0.00039159156324162234</t>
+          <t>0.00015698587127157548 +/- 0.0004086996167402487</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -3166,7 +3166,7 @@
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>-0.00026357406431209984 +/- 0.00026357406431209984</t>
+          <t>-0.00026357406431211096 +/- 0.00035362171494462914</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>0.01841688654353557 +/- 0.0022935423548391246</t>
+          <t>0.01846965699208438 +/- 0.002359966203166001</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
@@ -4586,7 +4586,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>-0.0009727626459143934 +/- 0.000922843675146411</t>
+          <t>-0.0009241245136186738 +/- 0.0008268482490272344</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
@@ -6136,7 +6136,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>0.019499017681728837 +/- 0.0012627662212360013</t>
+          <t>0.01944990176817284 +/- 0.0012656285586174045</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
@@ -7641,7 +7641,7 @@
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>0.003440038222646957 +/- 0.0015378382168591508</t>
+          <t>0.003392259913999085 +/- 0.0015474567358529944</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
+          <t>0.00497344278126508 +/- 0.0009669234376871551</t>
+        </is>
+      </c>
+      <c r="BZ11" t="inlineStr">
+        <is>
           <t>0.00502172863351037 +/- 0.0008955691449054423</t>
-        </is>
-      </c>
-      <c r="BZ11" t="inlineStr">
-        <is>
-          <t>0.00497344278126508 +/- 0.0009669234376871551</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
